--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-01T17:43:29.274Z</t>
+    <t>2026-07-16T20:46:22.455Z</t>
   </si>
   <si>
     <t>Global Healthcare Technology Leader | Medtronic (CA)</t>
